--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_pircc_pircc.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_pircc_pircc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J181"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +527,16 @@
           <t>020104</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -567,6 +587,16 @@
           <t>020104</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -617,6 +647,16 @@
           <t>020109</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -667,6 +707,16 @@
           <t>020109</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -717,6 +767,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -767,6 +827,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -817,6 +887,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -867,6 +947,16 @@
           <t>020201</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -917,6 +1007,16 @@
           <t>020202</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -967,6 +1067,16 @@
           <t>020202</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1017,6 +1127,16 @@
           <t>020202</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1067,6 +1187,16 @@
           <t>020203</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1117,6 +1247,16 @@
           <t>020204</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1167,6 +1307,16 @@
           <t>020205</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1217,6 +1367,16 @@
           <t>020304</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>UGEL ANTONIO RAYMONDI</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1267,6 +1427,16 @@
           <t>020504</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1317,6 +1487,16 @@
           <t>020510</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1367,6 +1547,16 @@
           <t>020513</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1417,6 +1607,16 @@
           <t>020513</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>UGEL BOLOGNESI</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1467,6 +1667,16 @@
           <t>020606</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1517,6 +1727,16 @@
           <t>020702</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>UGEL CARLOS FERMIN FITZCARRALD</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1567,6 +1787,16 @@
           <t>021005</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1617,6 +1847,16 @@
           <t>021103</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1667,6 +1907,16 @@
           <t>021104</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1717,6 +1967,16 @@
           <t>021105</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1767,6 +2027,16 @@
           <t>021204</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1817,6 +2087,16 @@
           <t>021204</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1867,6 +2147,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1917,6 +2207,16 @@
           <t>021206</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>UGEL HUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1967,6 +2267,16 @@
           <t>021302</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2017,6 +2327,16 @@
           <t>021302</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2065,6 +2385,16 @@
       <c r="J33" t="inlineStr">
         <is>
           <t>021302</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
         </is>
       </c>
     </row>
@@ -2097,6 +2427,8 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2147,6 +2479,16 @@
           <t>021404</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>UGEL OCROS</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2197,6 +2539,16 @@
           <t>021701</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2247,6 +2599,16 @@
           <t>021701</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2297,6 +2659,16 @@
           <t>021707</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2347,6 +2719,16 @@
           <t>021707</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2397,6 +2779,16 @@
           <t>021708</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2447,6 +2839,16 @@
           <t>021710</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>UGEL RECUAY</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2497,6 +2899,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2547,6 +2959,16 @@
           <t>021801</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2597,6 +3019,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2647,6 +3079,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2697,6 +3139,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2747,6 +3199,16 @@
           <t>022008</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2797,6 +3259,16 @@
           <t>110403</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>UGEL PALPA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2847,6 +3319,16 @@
           <t>130205</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2897,6 +3379,16 @@
           <t>130401</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2947,6 +3439,16 @@
           <t>130403</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>UGEL CHEPEN</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2997,6 +3499,16 @@
           <t>130601</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>UGEL OTUZCO</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3047,6 +3559,16 @@
           <t>130705</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>UGEL PACASMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3097,6 +3619,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3147,6 +3679,16 @@
           <t>131101</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>UGEL GRAN CHIMÚ</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3197,6 +3739,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3247,6 +3799,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3297,6 +3859,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3347,6 +3919,16 @@
           <t>140101</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3397,6 +3979,16 @@
           <t>140108</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3447,6 +4039,16 @@
           <t>140304</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3497,6 +4099,16 @@
           <t>140305</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3547,6 +4159,16 @@
           <t>140305</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3597,6 +4219,16 @@
           <t>140307</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3647,6 +4279,16 @@
           <t>140308</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3697,6 +4339,16 @@
           <t>140309</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3747,6 +4399,16 @@
           <t>140310</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3797,6 +4459,16 @@
           <t>150202</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3847,6 +4519,16 @@
           <t>150305</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>UGEL 11 CAJATAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3897,6 +4579,16 @@
           <t>150512</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3947,6 +4639,16 @@
           <t>150715</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3997,6 +4699,16 @@
           <t>150721</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4047,6 +4759,16 @@
           <t>151011</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>UGEL 13 YAUYOS</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4097,6 +4819,16 @@
           <t>151022</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>UGEL 13 YAUYOS</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4147,6 +4879,16 @@
           <t>200115</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4197,6 +4939,16 @@
           <t>200115</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4247,6 +4999,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4297,6 +5059,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4347,6 +5119,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4397,6 +5179,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4447,6 +5239,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4497,6 +5299,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4547,6 +5359,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4597,6 +5419,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4647,6 +5479,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4697,6 +5539,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4747,6 +5599,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4797,6 +5659,16 @@
           <t>200107</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4847,6 +5719,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4897,6 +5779,16 @@
           <t>200110</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4947,6 +5839,16 @@
           <t>200111</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4997,6 +5899,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5047,6 +5959,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5097,6 +6019,16 @@
           <t>200209</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5147,6 +6079,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5197,6 +6139,16 @@
           <t>200306</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5247,6 +6199,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5297,6 +6259,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5347,6 +6319,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5397,6 +6379,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -5447,6 +6439,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5497,6 +6499,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5547,6 +6559,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5597,6 +6619,16 @@
           <t>200410</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5647,6 +6679,16 @@
           <t>200604</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5697,6 +6739,16 @@
           <t>200604</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5747,6 +6799,16 @@
           <t>200701</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5797,6 +6859,16 @@
           <t>200701</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5847,6 +6919,16 @@
           <t>200804</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5897,6 +6979,16 @@
           <t>240203</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5947,6 +7039,16 @@
           <t>240203</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5997,6 +7099,16 @@
           <t>240105</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>UGEL TUMBES</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6047,6 +7159,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6097,6 +7219,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6147,6 +7279,16 @@
           <t>240202</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6197,6 +7339,16 @@
           <t>020901</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>UGEL CORONGO</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6247,6 +7399,16 @@
           <t>090609</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>UGEL HUAYTARÁ</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6297,6 +7459,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6347,6 +7519,16 @@
           <t>020604</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -6397,6 +7579,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -6447,6 +7639,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -6497,6 +7699,16 @@
           <t>020804</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>UGEL CASMA</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -6547,6 +7759,16 @@
           <t>090401</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>UGEL CASTROVIRREYNA</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -6597,6 +7819,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -6647,6 +7879,16 @@
           <t>020202</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>UGEL AIJA</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -6697,6 +7939,16 @@
           <t>200109</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6747,6 +7999,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6797,6 +8059,16 @@
           <t>200105</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6847,6 +8119,16 @@
           <t>200305</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6897,6 +8179,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -6947,6 +8239,16 @@
           <t>130201</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6997,6 +8299,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7047,6 +8359,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7097,6 +8419,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7147,6 +8479,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7197,6 +8539,16 @@
           <t>021809</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7247,6 +8599,16 @@
           <t>130702</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>UGEL PACASMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -7297,6 +8659,16 @@
           <t>150728</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -7347,6 +8719,16 @@
           <t>022001</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -7397,6 +8779,16 @@
           <t>021008</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -7447,6 +8839,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -7497,6 +8899,16 @@
           <t>200107</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -7547,6 +8959,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -7597,6 +9019,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -7647,6 +9079,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -7697,6 +9139,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -7747,6 +9199,16 @@
           <t>022005</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>UGEL YUNGAY</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -7797,6 +9259,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -7847,6 +9319,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7897,6 +9379,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -7947,6 +9439,16 @@
           <t>060112</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -7997,6 +9499,16 @@
           <t>200305</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8047,6 +9559,16 @@
           <t>200406</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8097,6 +9619,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8147,6 +9679,16 @@
           <t>200202</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8197,6 +9739,16 @@
           <t>200404</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -8247,6 +9799,16 @@
           <t>200111</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8297,6 +9859,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -8347,6 +9919,16 @@
           <t>140108</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -8397,6 +9979,16 @@
           <t>140312</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8447,6 +10039,16 @@
           <t>140312</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -8497,6 +10099,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8547,6 +10159,16 @@
           <t>130104</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8597,6 +10219,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -8647,6 +10279,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -8697,6 +10339,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -8747,6 +10399,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -8797,6 +10459,16 @@
           <t>200101</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -8847,6 +10519,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -8897,6 +10579,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -8947,6 +10639,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -8997,6 +10699,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9047,6 +10759,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -9097,6 +10819,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -9147,6 +10879,16 @@
           <t>200402</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9197,6 +10939,16 @@
           <t>200603</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -9247,6 +10999,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -9297,6 +11059,16 @@
           <t>131201</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -9347,6 +11119,16 @@
           <t>240203</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -9397,6 +11179,16 @@
           <t>240203</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>DRE TUMBES</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>UGEL CONTRALMIRANTE VILLAR</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -9445,6 +11237,16 @@
       <c r="J181" t="inlineStr">
         <is>
           <t>021005</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_pircc_pircc.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_pircc_pircc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L181"/>
+  <dimension ref="A1:M181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -537,6 +542,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -597,6 +607,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -657,6 +672,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -717,6 +737,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -777,6 +802,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -837,6 +867,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -897,6 +932,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -957,6 +997,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1017,6 +1062,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1077,6 +1127,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1137,6 +1192,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1197,6 +1257,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1257,6 +1322,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1317,6 +1387,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1377,6 +1452,11 @@
           <t>UGEL ANTONIO RAYMONDI</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1437,6 +1517,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1497,6 +1582,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1557,6 +1647,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1617,6 +1712,11 @@
           <t>UGEL BOLOGNESI</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1677,6 +1777,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1737,6 +1842,11 @@
           <t>UGEL CARLOS FERMIN FITZCARRALD</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1797,6 +1907,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1857,6 +1972,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1917,6 +2037,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1977,6 +2102,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2037,6 +2167,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2097,6 +2232,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2157,6 +2297,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2217,6 +2362,11 @@
           <t>UGEL HUAYLAS</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2277,6 +2427,11 @@
           <t>UGEL MARISCAL LUZURIAGA</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2337,6 +2492,11 @@
           <t>UGEL MARISCAL LUZURIAGA</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2397,6 +2557,11 @@
           <t>UGEL MARISCAL LUZURIAGA</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2422,13 +2587,42 @@
           <t>A CARGO DE UGRD - PRONIED</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>FIDEL OLIVAS ESCUDERO</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>021304</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2489,6 +2683,11 @@
           <t>UGEL OCROS</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2549,6 +2748,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2609,6 +2813,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2669,6 +2878,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2729,6 +2943,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2789,6 +3008,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2849,6 +3073,11 @@
           <t>UGEL RECUAY</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2909,6 +3138,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2969,6 +3203,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3029,6 +3268,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3089,6 +3333,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3149,6 +3398,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3209,6 +3463,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3269,6 +3528,11 @@
           <t>UGEL PALPA</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3329,6 +3593,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3389,6 +3658,11 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3449,6 +3723,11 @@
           <t>UGEL CHEPEN</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3509,6 +3788,11 @@
           <t>UGEL OTUZCO</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3569,6 +3853,11 @@
           <t>UGEL PACASMAYO</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3629,6 +3918,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3689,6 +3983,11 @@
           <t>UGEL GRAN CHIMÚ</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3749,6 +4048,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3809,6 +4113,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3869,6 +4178,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3929,6 +4243,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3989,6 +4308,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4049,6 +4373,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4109,6 +4438,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4169,6 +4503,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4229,6 +4568,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4289,6 +4633,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4349,6 +4698,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4409,6 +4763,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4469,6 +4828,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4529,6 +4893,11 @@
           <t>UGEL 11 CAJATAMBO</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4589,6 +4958,11 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4649,6 +5023,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4709,6 +5088,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4769,6 +5153,11 @@
           <t>UGEL 13 YAUYOS</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4829,6 +5218,11 @@
           <t>UGEL 13 YAUYOS</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4889,6 +5283,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4949,6 +5348,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5009,6 +5413,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5069,6 +5478,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5129,6 +5543,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5189,6 +5608,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5249,6 +5673,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5309,6 +5738,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5369,6 +5803,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5429,6 +5868,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5489,6 +5933,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5549,6 +5998,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5609,6 +6063,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5669,6 +6128,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5729,6 +6193,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5789,6 +6258,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5849,6 +6323,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5909,6 +6388,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5969,6 +6453,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6029,6 +6518,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6089,6 +6583,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6149,6 +6648,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6209,6 +6713,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6269,6 +6778,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6329,6 +6843,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6389,6 +6908,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6449,6 +6973,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6509,6 +7038,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6569,6 +7103,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6629,6 +7168,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6689,6 +7233,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6749,6 +7298,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6809,6 +7363,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6869,6 +7428,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6929,6 +7493,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6989,6 +7558,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7049,6 +7623,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7109,6 +7688,11 @@
           <t>UGEL TUMBES</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7169,6 +7753,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7229,6 +7818,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7289,6 +7883,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7349,6 +7948,11 @@
           <t>UGEL CORONGO</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7409,6 +8013,11 @@
           <t>UGEL HUAYTARÁ</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7469,6 +8078,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7529,6 +8143,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7589,6 +8208,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7649,6 +8273,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7709,6 +8338,11 @@
           <t>UGEL CASMA</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7769,6 +8403,11 @@
           <t>UGEL CASTROVIRREYNA</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7829,6 +8468,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7889,6 +8533,11 @@
           <t>UGEL AIJA</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7949,6 +8598,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -8009,6 +8663,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -8069,6 +8728,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8129,6 +8793,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8189,6 +8858,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8249,6 +8923,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8309,6 +8988,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8369,6 +9053,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8429,6 +9118,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8489,6 +9183,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8549,6 +9248,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8609,6 +9313,11 @@
           <t>UGEL PACASMAYO</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8669,6 +9378,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8729,6 +9443,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8789,6 +9508,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8849,6 +9573,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8909,6 +9638,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8969,6 +9703,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -9029,6 +9768,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -9089,6 +9833,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -9149,6 +9898,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -9209,6 +9963,11 @@
           <t>UGEL YUNGAY</t>
         </is>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -9269,6 +10028,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -9329,6 +10093,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -9389,6 +10158,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -9449,6 +10223,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -9509,6 +10288,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -9569,6 +10353,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9629,6 +10418,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9689,6 +10483,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9749,6 +10548,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9809,6 +10613,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9869,6 +10678,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9929,6 +10743,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9989,6 +10808,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -10049,6 +10873,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -10109,6 +10938,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -10169,6 +11003,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -10229,6 +11068,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -10289,6 +11133,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -10349,6 +11198,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -10409,6 +11263,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -10469,6 +11328,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -10529,6 +11393,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -10589,6 +11458,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -10649,6 +11523,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10709,6 +11588,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10769,6 +11653,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10829,6 +11718,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10889,6 +11783,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10949,6 +11848,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -11009,6 +11913,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -11069,6 +11978,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -11129,6 +12043,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -11189,6 +12108,11 @@
           <t>UGEL CONTRALMIRANTE VILLAR</t>
         </is>
       </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>UGRD</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -11247,6 +12171,11 @@
       <c r="L181" t="inlineStr">
         <is>
           <t>UGEL HUARI</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>UGRD</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_pircc_pircc.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_pircc_pircc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:O181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,16 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -544,6 +554,16 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>86056 DANIEL ALCIDES CARRION/86056 DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -609,6 +629,16 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>86057</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -674,6 +704,16 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>86053</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -739,6 +779,16 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>86105</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -804,6 +854,16 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -869,6 +929,16 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>86135</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -934,6 +1004,16 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>86852</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -999,6 +1079,16 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>86852</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1064,6 +1154,16 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1129,6 +1229,16 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1194,6 +1304,16 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>86153</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1259,6 +1379,16 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>86161/86161</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1324,6 +1454,16 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>86167/86167</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1389,6 +1529,16 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1454,6 +1604,16 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>86179/86179</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1519,6 +1679,16 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>86218</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1584,6 +1754,16 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>86232</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1649,6 +1829,16 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1714,6 +1904,16 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1779,6 +1979,16 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>86307 TEOFILO CASTILLO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1844,6 +2054,16 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1909,6 +2129,16 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>86416</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -1974,6 +2204,16 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>88123</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2039,6 +2279,16 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>026</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2104,6 +2354,16 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2169,6 +2429,16 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>86529 ALFONSO UGARTE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2234,6 +2504,16 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
+          <t>86529 ALFONSO UGARTE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2299,6 +2579,16 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
+          <t>86825/86825</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2364,6 +2654,16 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>88371</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2429,6 +2729,16 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>075 TEODOSIO TARAZONA VIDAL</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2494,6 +2804,16 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
+          <t>84129 LOS ALISOS</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2559,6 +2879,16 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
+          <t>84139 CIRILO CALIXTO FELIPE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2620,6 +2950,16 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>84152 ULISES LLANOS OLIVEROS</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2685,6 +3025,16 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
+          <t>20485</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2750,6 +3100,16 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2815,6 +3175,16 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2880,6 +3250,16 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -2945,6 +3325,16 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3010,6 +3400,16 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
+          <t>86963</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3075,6 +3475,16 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
+          <t>86570 SANTO DOMINGO DE COMPINA</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3140,6 +3550,16 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
+          <t>88005 CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3205,6 +3625,16 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>88040</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3270,6 +3700,16 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>86749/86749</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3335,6 +3775,16 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
+          <t>86969</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3400,6 +3850,16 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
+          <t>86747/86747</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3465,6 +3925,16 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3530,6 +4000,16 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
+          <t>22432/22432</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3595,6 +4075,16 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>80083</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3660,6 +4150,16 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
+          <t>80395/80395</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3725,6 +4225,16 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
+          <t>80913</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3790,6 +4300,16 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
+          <t>81632</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3855,6 +4375,16 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
+          <t>1821 SANTA ROSA DE LIMA</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3920,6 +4450,16 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -3985,6 +4525,16 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
+          <t>82613</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4050,6 +4600,16 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
+          <t>81754</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4115,6 +4675,16 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
+          <t>80093 JOSE OLAYA/80093 JOSE OLAYA</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4180,6 +4750,16 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
+          <t>80093 JOSE OLAYA/80093 JOSE OLAYA</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4245,6 +4825,16 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
+          <t>10024 NUESTRA SEÑORA DE FATIMA/10024 NUESTRA SEÑORA DE FATIMA/10024 NUESTRA SEÑORA DE FATIMA</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4310,6 +4900,16 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
+          <t>10036 MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4375,6 +4975,16 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>VICTOR MONTERO KOSSUTH</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4440,6 +5050,16 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
+          <t>11238</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4505,6 +5125,16 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
+          <t>11238</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4570,6 +5200,16 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
+          <t>10150 SANTOS CARDENAS VALLADARES/10150 SANTOS CARDENAS VALLADARES</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4635,6 +5275,16 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>10190</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4700,6 +5350,16 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
+          <t>10998 SANTISIMA TRINIDAD</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4765,6 +5425,16 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
+          <t>10779 GENERAL OSCAR RAIMUNDO BENAVIDES LARREA</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4830,6 +5500,16 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4895,6 +5575,16 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -4960,6 +5650,16 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
+          <t>20176/20176</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5025,6 +5725,16 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
+          <t>20648</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5090,6 +5800,16 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
+          <t>20590 SANTA MARIA/20590 SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5155,6 +5875,16 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
+          <t>20723/20723</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5220,6 +5950,16 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
+          <t>20950</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5285,6 +6025,16 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
+          <t>016 EMILIA BARCIA BONIFFATTI</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5350,6 +6100,16 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
+          <t>032 APRENDIZAJE</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5415,6 +6175,16 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
+          <t>20140</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5480,6 +6250,16 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
+          <t>20140</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5545,6 +6325,16 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI LACHIRA</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5610,6 +6400,16 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
+          <t>14038/14038</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5675,6 +6475,16 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
+          <t>14041</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5740,6 +6550,16 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
+          <t>14057/14057</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5805,6 +6625,16 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
+          <t>15324/15324/15324</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5870,6 +6700,16 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
+          <t>20073</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -5935,6 +6775,16 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
+          <t>20151</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6000,6 +6850,16 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
+          <t>20232/20232</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6065,6 +6925,16 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
+          <t>20232/20232</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6130,6 +7000,16 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
+          <t>20234</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6195,6 +7075,16 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6260,6 +7150,16 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
+          <t>14989</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6325,6 +7225,16 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
+          <t>14888/14888</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6390,6 +7300,16 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
+          <t>15219</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6455,6 +7375,16 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
+          <t>20007</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6520,6 +7450,16 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6585,6 +7525,16 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
+          <t>15189</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6650,6 +7600,16 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
+          <t>15157/15157/15157</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6715,6 +7675,16 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
+          <t>15419/15419</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6780,6 +7750,16 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6845,6 +7825,16 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
+          <t>14639</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6910,6 +7900,16 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
+          <t>20053</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -6975,6 +7975,16 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
+          <t>15435 DIEGO FERRE</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7040,6 +8050,16 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
+          <t>15435 DIEGO FERRE</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7105,6 +8125,16 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
+          <t>20225</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7170,6 +8200,16 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
+          <t>14687</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7235,6 +8275,16 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
+          <t>15250/15250/15250</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7300,6 +8350,16 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
+          <t>15286</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7365,6 +8425,16 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
+          <t>15038 SANTA ROSA DE LIMA/15038 SANTA ROSA DE LIMA/15038 SANTA ROSA DE LIMA</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7430,6 +8500,16 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
+          <t>JABONILLAL</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7495,6 +8575,16 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
+          <t>15196</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7560,6 +8650,16 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
+          <t>068 MARIA MUÑOZ DE MEDINA</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7625,6 +8725,16 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
+          <t>068 MARIA MUÑOZ DE MEDINA</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7690,6 +8800,16 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7755,6 +8875,16 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
+          <t>074 HILARIO MONTOYA SALDARRIAGA</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7820,6 +8950,16 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7885,6 +9025,16 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -7950,6 +9100,16 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
+          <t>88127</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8015,6 +9175,16 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8080,6 +9250,16 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
+          <t>20808/20808</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8145,6 +9325,16 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
+          <t>86311/86311</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8210,6 +9400,16 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
+          <t>86651</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8275,6 +9475,16 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
+          <t>88398</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8340,6 +9550,16 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
+          <t>88113/88113</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8405,6 +9625,16 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8470,6 +9700,16 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
+          <t>11590 JUAN PABLO II</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8535,6 +9775,16 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
+          <t>86153</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8600,6 +9850,16 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8665,6 +9925,16 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8730,6 +10000,16 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8795,6 +10075,16 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8860,6 +10150,16 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8925,6 +10225,16 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
+          <t>JUAN BASILIO VILLALOBOS/JUAN BASILIO VILLALOBOS</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -8990,6 +10300,16 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9055,6 +10375,16 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9120,6 +10450,16 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9185,6 +10525,16 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9250,6 +10600,16 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9315,6 +10675,16 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9380,6 +10750,16 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
+          <t>VIRGEN DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9445,6 +10825,16 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
+          <t>89539 SANTA ROSA DE CAYASBAMBA/89539 SANTA ROSA DE CAYASBAMBA</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9510,6 +10900,16 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
+          <t>86432</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9575,6 +10975,16 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9640,6 +11050,16 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
+          <t>1154</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9705,6 +11125,16 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
+          <t>1193</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9770,6 +11200,16 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9835,6 +11275,16 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9900,6 +11350,16 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -9965,6 +11425,16 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10030,6 +11500,16 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
+          <t>2175</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10095,6 +11575,16 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10160,6 +11650,16 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10225,6 +11725,16 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10290,6 +11800,16 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10355,6 +11875,16 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10420,6 +11950,16 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10485,6 +12025,16 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10550,6 +12100,16 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10615,6 +12175,16 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10680,6 +12250,16 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
+          <t>20863/20863</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10745,6 +12325,16 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10810,6 +12400,16 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
+          <t>510 BLANCA VALERA GONZALES</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10875,6 +12475,16 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
+          <t>510 BLANCA VALERA GONZALES</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -10940,6 +12550,16 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11005,6 +12625,16 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11070,6 +12700,16 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11135,6 +12775,16 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11200,6 +12850,16 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11265,6 +12925,16 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11330,6 +13000,16 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11395,6 +13075,16 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11460,6 +13150,16 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11525,6 +13225,16 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11590,6 +13300,16 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11655,6 +13375,16 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
+          <t>EL CARMELO</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11720,6 +13450,16 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11785,6 +13525,16 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11850,6 +13600,16 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
+          <t>1596</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11915,6 +13675,16 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -11980,6 +13750,16 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12045,6 +13825,16 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12110,6 +13900,16 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
           <t>UGRD</t>
         </is>
       </c>
@@ -12174,6 +13974,16 @@
         </is>
       </c>
       <c r="M181" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
         <is>
           <t>UGRD</t>
         </is>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_pircc_pircc.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_ugrd_pircc_pircc.xlsx
@@ -419,27 +419,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Código Local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>CUI</t>
+          <t>cui</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Tipo de intervención (MBR o ME)</t>
+          <t>tipo_de_intervencion_mbr_o_me</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
